--- a/medical_surveys_questionnaires/050_safety_observation_checklist--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/050_safety_observation_checklist--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -868,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'direct_observation'}</t>
+          <t>direct_observation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Direct Observation'}</t>
+          <t>Direct Observation</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'review_of_record'}</t>
+          <t>review_of_record</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Review of Record'}</t>
+          <t>Review of Record</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'conducted'}</t>
+          <t>conducted</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Conducted'}</t>
+          <t>Conducted</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'not_conducted'}</t>
+          <t>not_conducted</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Not Conducted'}</t>
+          <t>Not Conducted</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'administered'}</t>
+          <t>administered</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Administered'}</t>
+          <t>Administered</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'not_administered'}</t>
+          <t>not_administered</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Not Administered'}</t>
+          <t>Not Administered</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'stable'}</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Stable'}</t>
+          <t>Stable</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'unstable'}</t>
+          <t>unstable</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Unstable'}</t>
+          <t>Unstable</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'stable'}</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Stable'}</t>
+          <t>Stable</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'unstable'}</t>
+          <t>unstable</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Unstable'}</t>
+          <t>Unstable</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'complete'}</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Complete'}</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'stable'}</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Stable'}</t>
+          <t>Stable</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'stable'}</t>
+          <t>unstable</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Stable'}</t>
+          <t>Unstable</t>
         </is>
       </c>
     </row>
@@ -1343,29 +1343,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'unstable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Unstable'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>patient_status_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>{'label':_'not_applicable'}</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>{'label': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
